--- a/grading_results_rag_test_metrics.xlsx
+++ b/grading_results_rag_test_metrics.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\rag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UEH\Downloads\17. Đề án tốt nghiệp\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C88E1F-1A35-4342-8F35-4CCB6052859B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8317D39-8896-465B-BAB7-60D83D367835}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
   <si>
     <t>Chiến lược kinh doanh thương mại điện tử</t>
   </si>
@@ -341,6 +341,30 @@
 Trà Hồng Đoan Nhi - 31211020138 - nhóm trưởng 
 Nguyễn Thị Hồng Nhung - 31211027984 
 Nguyễn Thị Quỳnh Như - ...</t>
+  </si>
+  <si>
+    <t>GIỎI</t>
+  </si>
+  <si>
+    <t>&gt;8</t>
+  </si>
+  <si>
+    <t>KHÁ</t>
+  </si>
+  <si>
+    <t>6.5-7.9</t>
+  </si>
+  <si>
+    <t>TRUNG BÌNH</t>
+  </si>
+  <si>
+    <t>5-6.4</t>
+  </si>
+  <si>
+    <t>YẾU</t>
+  </si>
+  <si>
+    <t>&lt;5</t>
   </si>
 </sst>
 </file>
@@ -376,9 +400,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -683,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
@@ -691,9 +718,11 @@
     <col min="3" max="3" width="51.5703125" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -709,8 +738,14 @@
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -720,14 +755,27 @@
       <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="str">
+        <f>IF(E2&gt;8,"GIỎI", IF(E2&gt;=6.5,"KHÁ", IF(E2&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+      <c r="H2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -737,14 +785,27 @@
       <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="1">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F17" si="0">IF(E3&gt;8,"GIỎI", IF(E3&gt;=6.5,"KHÁ", IF(E3&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+      <c r="H3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -754,14 +815,24 @@
       <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -771,14 +842,18 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>6</v>
       </c>
       <c r="E5" s="1">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -788,14 +863,24 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -805,14 +890,24 @@
       <c r="C7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -822,14 +917,18 @@
       <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -839,14 +938,18 @@
       <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>TRUNG BÌNH</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -856,14 +959,18 @@
       <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="1">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -873,14 +980,18 @@
       <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="1">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -890,14 +1001,18 @@
       <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E12" s="1">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>TRUNG BÌNH</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -907,14 +1022,18 @@
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -924,14 +1043,18 @@
       <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
         <v>5.2</v>
       </c>
       <c r="E14" s="1">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -941,14 +1064,18 @@
       <c r="C15" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E15" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -958,14 +1085,18 @@
       <c r="C16" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>7.4</v>
       </c>
       <c r="E16" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -975,14 +1106,184 @@
       <c r="C17" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="1">
         <v>6.5</v>
       </c>
+      <c r="F17" t="str">
+        <f>IF(E17&gt;8,"GIỎI", IF(E17&gt;=6.5,"KHÁ", IF(E17&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20" t="str">
+        <f>IF(G20&gt;8,"GIỎI", IF(G20&gt;=6.5,"KHÁ", IF(G20&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>TRUNG BÌNH</v>
+      </c>
+      <c r="J20" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20">
+        <f>COUNTIF($H$20:$H$35,J20)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" ref="H21:H35" si="1">IF(G21&gt;8,"GIỎI", IF(G21&gt;=6.5,"KHÁ", IF(G21&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>YẾU</v>
+      </c>
+      <c r="J21" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21">
+        <f>COUNTIF($H$20:$H$35,J21)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>7.3</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22">
+        <f>COUNTIF($H$20:$H$35,J22)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>6</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v>TRUNG BÌNH</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="1"/>
+        <v>TRUNG BÌNH</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <v>7.3</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>7.2</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <v>7.5</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>7.6</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>7.8</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>6.8</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G31">
+        <v>7.5</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <v>5.2</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="1"/>
+        <v>TRUNG BÌNH</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <v>6.2</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v>TRUNG BÌNH</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G34">
+        <v>7.4</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="1"/>
+        <v>YẾU</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>